--- a/outputs/daily/hr_rankings_2026-10-19_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-19_remaining.xlsx
@@ -760,19 +760,31 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>53.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -786,65 +798,61 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -881,7 +889,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -954,14 +962,46 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1000,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1008,11 +1048,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>52.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1026,65 +1078,61 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>48.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
         <v>28.9</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -1121,7 +1169,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1194,14 +1242,46 @@
           <t>0.1639</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1240,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1264,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.7</v>
+        <v>51.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1278,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1288,10 +1368,10 @@
         <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1301,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1476,8 +1552,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1516,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1540,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.6</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1554,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1564,10 +1648,10 @@
         <v>33.4</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1577,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1752,8 +1832,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1767,12 +1855,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1792,19 +1880,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>46.4</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1818,65 +1918,61 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1893,27 +1989,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1923,77 +2019,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>0.2134</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2007,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -2032,19 +2160,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>45.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2058,65 +2198,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2133,12 +2269,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2148,12 +2284,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2163,77 +2299,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1288</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>0.1803</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2247,24 +2415,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -2272,22 +2440,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2296,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2310,62 +2478,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2385,12 +2549,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2400,12 +2564,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2415,101 +2579,109 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2528,7 +2700,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2548,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2572,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.5</v>
+        <v>44.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2586,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2596,10 +2768,10 @@
         <v>31.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -2609,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2784,8 +2952,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2824,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2848,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2862,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -2872,10 +3048,10 @@
         <v>31.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -2885,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3060,8 +3232,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3075,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -3100,19 +3280,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>37.9</v>
+        <v>39.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3126,65 +3318,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>10.6</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>70.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3201,27 +3389,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3231,77 +3419,109 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3315,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -3340,22 +3560,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3364,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.9</v>
+        <v>38</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3378,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3453,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3468,12 +3684,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3483,101 +3699,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3616,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3640,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.9</v>
+        <v>37.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3654,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3664,10 +3888,10 @@
         <v>33.4</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -3677,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3852,8 +4072,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3867,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -3892,19 +4120,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>33.9</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3918,65 +4158,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>23.3</v>
+        <v>13.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>31.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8</v>
+        <v>72.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -3993,27 +4229,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4023,77 +4259,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1044</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4107,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4132,19 +4400,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>32.9</v>
+        <v>34.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4158,65 +4438,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>12.8</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>18.3</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4233,27 +4509,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4263,77 +4539,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1186</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4347,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -4372,22 +4680,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4396,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.3</v>
+        <v>34.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4410,62 +4718,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>13.7</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>72.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4490,7 +4794,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4505,7 +4809,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4515,101 +4819,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4623,24 +4935,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -4648,22 +4960,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4672,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.3</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4686,62 +4998,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4761,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -4776,12 +5084,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -4791,101 +5099,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4899,24 +5215,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -4924,19 +5240,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>30.3</v>
+        <v>32.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4950,65 +5278,61 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5025,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5040,12 +5364,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5055,77 +5379,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>0.0707</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5164,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5172,11 +5528,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>29.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5190,20 +5558,20 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5213,42 +5581,38 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5285,7 +5649,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5358,14 +5722,46 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5730,19 +6126,31 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>53.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5756,65 +6164,61 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -5851,7 +6255,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -5924,14 +6328,46 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5970,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5978,11 +6414,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>52.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5996,65 +6444,61 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>48.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
         <v>28.9</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -6091,7 +6535,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -6164,14 +6608,46 @@
           <t>0.1639</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6210,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6234,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.7</v>
+        <v>51.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6248,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6258,10 +6734,10 @@
         <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6271,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6446,8 +6918,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6486,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6510,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.6</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6524,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6534,10 +7014,10 @@
         <v>33.4</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6547,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6722,8 +7198,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6737,12 +7221,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6762,19 +7246,31 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>46.4</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6788,65 +7284,61 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -6863,27 +7355,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -6893,77 +7385,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>0.2134</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6977,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -7002,19 +7526,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>45.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7028,65 +7564,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7103,12 +7635,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7118,12 +7650,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7133,77 +7665,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1288</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>0.1803</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7217,24 +7781,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -7242,22 +7806,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7266,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7280,62 +7844,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7355,12 +7915,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7370,12 +7930,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7385,101 +7945,109 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7498,7 +8066,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7518,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -7542,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.5</v>
+        <v>44.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -7556,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -7566,10 +8134,10 @@
         <v>31.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -7579,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7754,8 +8318,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7794,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -7818,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -7832,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -7842,10 +8414,10 @@
         <v>31.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -7855,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8030,8 +8598,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8045,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -8070,19 +8646,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>37.9</v>
+        <v>39.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8096,65 +8684,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>10.6</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>70.59999999999999</v>
+        <v>12</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8171,27 +8755,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8201,77 +8785,109 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8285,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -8310,22 +8926,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -8334,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.9</v>
+        <v>38</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8348,65 +8964,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8423,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8438,12 +9050,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8453,101 +9065,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8586,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -8610,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.9</v>
+        <v>37.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8624,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -8634,10 +9254,10 @@
         <v>33.4</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -8647,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8822,8 +9438,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8837,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -8862,19 +9486,31 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>33.9</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8888,65 +9524,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>23.3</v>
+        <v>13.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>31.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8</v>
+        <v>72.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -8963,27 +9595,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -8993,77 +9625,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1044</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9077,12 +9741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9102,19 +9766,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>32.9</v>
+        <v>34.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9128,65 +9804,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>12.8</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>18.3</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9203,27 +9875,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9233,77 +9905,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1186</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9317,24 +10021,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -9342,22 +10046,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9366,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.3</v>
+        <v>34.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9380,62 +10084,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>13.7</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>72.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9460,7 +10160,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -9475,7 +10175,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -9485,101 +10185,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9593,24 +10301,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -9618,22 +10326,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -9642,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.3</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9656,62 +10364,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9731,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -9746,12 +10450,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -9761,101 +10465,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9869,24 +10581,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -9894,19 +10606,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>30.3</v>
+        <v>32.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9920,65 +10644,61 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -9995,12 +10715,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10010,12 +10730,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10025,77 +10745,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>0.0707</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10134,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10142,11 +10894,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>29.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10160,20 +10924,20 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10183,42 +10947,38 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -10255,7 +11015,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10328,14 +11088,46 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
